--- a/fixtures/demo-clients.xlsx
+++ b/fixtures/demo-clients.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="77">
   <si>
     <t>רשימת לקוחות — משרד רו"ח (נתוני הדגמה בדויים)</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>טלפון</t>
+  </si>
+  <si>
+    <t>תעריף</t>
   </si>
   <si>
     <t>סטטוס</t>
@@ -619,10 +622,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="17" width="14" customWidth="1"/>
+    <col min="1" max="18" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -630,7 +633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -682,8 +685,11 @@
       <c r="Q2" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="R2" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -691,52 +697,55 @@
         <v>234567891</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3">
         <v>234567909</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L3">
         <v>6.5</v>
       </c>
       <c r="M3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q3" t="s">
         <v>27</v>
       </c>
+      <c r="Q3">
+        <v>1200</v>
+      </c>
+      <c r="R3" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -744,52 +753,55 @@
         <v>515000002</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P4" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>27</v>
+        <v>34</v>
+      </c>
+      <c r="Q4">
+        <v>950</v>
+      </c>
+      <c r="R4" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -797,52 +809,55 @@
         <v>234567902</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5">
         <v>4</v>
       </c>
       <c r="M5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P5" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>27</v>
+        <v>38</v>
+      </c>
+      <c r="Q5">
+        <v>1600</v>
+      </c>
+      <c r="R5" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -850,52 +865,55 @@
         <v>234567913</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6">
         <v>234567924</v>
       </c>
       <c r="I6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L6">
         <v>8</v>
       </c>
       <c r="M6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>27</v>
+        <v>43</v>
+      </c>
+      <c r="Q6">
+        <v>1800</v>
+      </c>
+      <c r="R6" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -903,52 +921,55 @@
         <v>234567924</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H7">
         <v>234567913</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P7" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>27</v>
+        <v>46</v>
+      </c>
+      <c r="Q7">
+        <v>1500</v>
+      </c>
+      <c r="R7" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -956,52 +977,55 @@
         <v>515000006</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P8" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>27</v>
+        <v>50</v>
+      </c>
+      <c r="Q8">
+        <v>2500</v>
+      </c>
+      <c r="R8" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1009,52 +1033,55 @@
         <v>234567946</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P9" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>27</v>
+        <v>54</v>
+      </c>
+      <c r="Q9">
+        <v>700</v>
+      </c>
+      <c r="R9" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1062,52 +1089,55 @@
         <v>234567957</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L10">
         <v>5</v>
       </c>
       <c r="M10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P10" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>27</v>
+        <v>58</v>
+      </c>
+      <c r="Q10">
+        <v>1100</v>
+      </c>
+      <c r="R10" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1115,52 +1145,55 @@
         <v>515000009</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P11" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>27</v>
+        <v>62</v>
+      </c>
+      <c r="Q11">
+        <v>2200</v>
+      </c>
+      <c r="R11" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1168,52 +1201,55 @@
         <v>234567979</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L12">
         <v>3</v>
       </c>
       <c r="M12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P12" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>27</v>
+        <v>66</v>
+      </c>
+      <c r="Q12">
+        <v>900</v>
+      </c>
+      <c r="R12" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1221,52 +1257,55 @@
         <v>234567980</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L13">
         <v>7</v>
       </c>
       <c r="M13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P13" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>27</v>
+        <v>70</v>
+      </c>
+      <c r="Q13">
+        <v>1300</v>
+      </c>
+      <c r="R13" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1274,102 +1313,108 @@
         <v>234567991</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P14" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>27</v>
+        <v>74</v>
+      </c>
+      <c r="Q14">
+        <v>850</v>
+      </c>
+      <c r="R14" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q15" t="s">
-        <v>27</v>
+        <v>24</v>
+      </c>
+      <c r="R15" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
